--- a/docs/build/lakeshore-enterprise-context/source/09_servicenow_support_workload/ticket_aging.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/09_servicenow_support_workload/ticket_aging.xlsx
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>394</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4">
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>353</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>166</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>96</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>292</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
